--- a/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
+++ b/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
   <si>
     <t xml:space="preserve">Caso de Teste</t>
   </si>
@@ -92,7 +92,13 @@
     <t xml:space="preserve">Exibe apenas pacientes com "Maria" no nome</t>
   </si>
   <si>
-    <t xml:space="preserve">2 resultados encontrados</t>
+    <t xml:space="preserve">Filtro de busca inexistente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Não existe um filtro de busca</t>
   </si>
   <si>
     <t xml:space="preserve">CT03 - Filtrar por Status (Inativos)</t>
@@ -110,7 +116,7 @@
     <t xml:space="preserve">Exibe apenas pacientes inativos</t>
   </si>
   <si>
-    <t xml:space="preserve">3 pacientes inativos listados</t>
+    <t xml:space="preserve">- Não existe um filtro de busca </t>
   </si>
   <si>
     <t xml:space="preserve">CT04 - Paginação de Resultados</t>
@@ -147,7 +153,10 @@
     <t xml:space="preserve">Lista reordenada (crescente/decrescente)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ordenação por idade correta</t>
+    <t xml:space="preserve">Filtro de busca por idade inexistente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Não existe este filtro por idade ao clicar</t>
   </si>
   <si>
     <t xml:space="preserve">CT06 - Visualizar Detalhes</t>
@@ -165,7 +174,10 @@
     <t xml:space="preserve">Abre página de detalhes com histórico completo</t>
   </si>
   <si>
-    <t xml:space="preserve">Perfil carregado com todos os dados</t>
+    <t xml:space="preserve">Pagina de histórico do paciente inexistente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Não ha uma pagina de historico do paciente </t>
   </si>
   <si>
     <t xml:space="preserve">CT07 - Listagem Vazia</t>
@@ -216,7 +228,7 @@
     <t xml:space="preserve">Exibe erro 403 (Proibido)</t>
   </si>
   <si>
-    <t xml:space="preserve">Acesso bloqueado</t>
+    <t xml:space="preserve">Pagina abre normalmente</t>
   </si>
   <si>
     <t xml:space="preserve">CT10 - Responsividade (Mobile)</t>
@@ -359,12 +371,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="32.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.01"/>
@@ -431,7 +443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="28.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -454,62 +466,62 @@
         <v>23</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>16</v>
@@ -518,85 +530,85 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="28.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>16</v>
@@ -607,25 +619,25 @@
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="E9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>16</v>
@@ -636,25 +648,25 @@
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>16</v>
@@ -665,25 +677,25 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>16</v>

--- a/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
+++ b/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -174,10 +174,10 @@
     <t xml:space="preserve">Abre página de detalhes com histórico completo</t>
   </si>
   <si>
-    <t xml:space="preserve">Pagina de histórico do paciente inexistente </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Não ha uma pagina de historico do paciente </t>
+    <t xml:space="preserve">Pagina de histórico do paciente exibida corretamente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
   </si>
   <si>
     <t xml:space="preserve">CT07 - Listagem Vazia</t>
@@ -346,15 +346,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -370,13 +370,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="32.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.01"/>
@@ -582,7 +688,7 @@
         <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>51</v>

--- a/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
+++ b/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
   <si>
     <t xml:space="preserve">Caso de Teste</t>
   </si>
@@ -92,7 +92,13 @@
     <t xml:space="preserve">Exibe apenas pacientes com "Maria" no nome</t>
   </si>
   <si>
-    <t xml:space="preserve">2 resultados encontrados</t>
+    <t xml:space="preserve">Filtro de busca inexistente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Não existe um filtro de busca</t>
   </si>
   <si>
     <t xml:space="preserve">CT03 - Filtrar por Status (Inativos)</t>
@@ -110,7 +116,7 @@
     <t xml:space="preserve">Exibe apenas pacientes inativos</t>
   </si>
   <si>
-    <t xml:space="preserve">3 pacientes inativos listados</t>
+    <t xml:space="preserve">- Não existe um filtro de busca </t>
   </si>
   <si>
     <t xml:space="preserve">CT04 - Paginação de Resultados</t>
@@ -147,7 +153,10 @@
     <t xml:space="preserve">Lista reordenada (crescente/decrescente)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ordenação por idade correta</t>
+    <t xml:space="preserve">Filtro de busca por idade inexistente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Não existe este filtro por idade ao clicar</t>
   </si>
   <si>
     <t xml:space="preserve">CT06 - Visualizar Detalhes</t>
@@ -165,7 +174,10 @@
     <t xml:space="preserve">Abre página de detalhes com histórico completo</t>
   </si>
   <si>
-    <t xml:space="preserve">Perfil carregado com todos os dados</t>
+    <t xml:space="preserve">Pagina de histórico do paciente exibida corretamente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
   </si>
   <si>
     <t xml:space="preserve">CT07 - Listagem Vazia</t>
@@ -216,7 +228,7 @@
     <t xml:space="preserve">Exibe erro 403 (Proibido)</t>
   </si>
   <si>
-    <t xml:space="preserve">Acesso bloqueado</t>
+    <t xml:space="preserve">Pagina abre normalmente</t>
   </si>
   <si>
     <t xml:space="preserve">CT10 - Responsividade (Mobile)</t>
@@ -334,15 +346,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -356,6 +368,112 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -431,7 +549,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="28.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -454,62 +572,62 @@
         <v>23</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>16</v>
@@ -518,85 +636,85 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="28.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>16</v>
@@ -607,25 +725,25 @@
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="E9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>16</v>
@@ -636,25 +754,25 @@
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>16</v>
@@ -665,25 +783,25 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>16</v>

--- a/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
+++ b/documentação/Testes/Caso de Teste/UC14 - LISTAR PACIENTES.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
   <si>
     <t xml:space="preserve">Caso de Teste</t>
   </si>
@@ -101,24 +101,6 @@
     <t xml:space="preserve">- Não existe um filtro de busca</t>
   </si>
   <si>
-    <t xml:space="preserve">CT03 - Filtrar por Status (Inativos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar exibição de inativos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usuário com permissão de gestor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Selecionar filtro "Status: Inativos"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exibe apenas pacientes inativos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Não existe um filtro de busca </t>
-  </si>
-  <si>
     <t xml:space="preserve">CT04 - Paginação de Resultados</t>
   </si>
   <si>
@@ -136,27 +118,6 @@
   </si>
   <si>
     <t xml:space="preserve">Paginação funcionando corretamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT05 - Ordenar por Idade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validar ordenação por idade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista carregada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar no cabeçalho "Idade"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista reordenada (crescente/decrescente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtro de busca por idade inexistente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Não existe este filtro por idade ao clicar</t>
   </si>
   <si>
     <t xml:space="preserve">CT06 - Visualizar Detalhes</t>
@@ -598,13 +559,13 @@
         <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -633,36 +594,36 @@
         <v>16</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="28.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -676,45 +637,45 @@
         <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>16</v>
@@ -725,25 +686,25 @@
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="E9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>16</v>
@@ -752,64 +713,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
